--- a/data/trans_orig/P47A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P47A-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción del peso respecto de su talla en 2007</t>
+          <t>Población según su autopercepción del peso respecto de su talla en 2007 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28363</t>
+          <t>28401</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55859</t>
+          <t>55390</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17590</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38403</t>
+          <t>37716</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51489</t>
+          <t>52238</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84791</t>
+          <t>85337</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>552797</t>
+          <t>554891</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>617800</t>
+          <t>614548</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>523332</t>
+          <t>525147</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>595939</t>
+          <t>595036</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1095244</t>
+          <t>1093069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1190883</t>
+          <t>1190169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,9%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>264712</t>
+          <t>268791</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>320609</t>
+          <t>323342</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>429795</t>
+          <t>429441</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>499192</t>
+          <t>497188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>712605</t>
+          <t>711403</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>801219</t>
+          <t>802084</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91765</t>
+          <t>93617</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>131159</t>
+          <t>135285</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>237245</t>
+          <t>237175</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>296598</t>
+          <t>296712</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>340163</t>
+          <t>341360</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>410067</t>
+          <t>410878</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56690</t>
+          <t>55736</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90160</t>
+          <t>92140</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52765</t>
+          <t>52555</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>86710</t>
+          <t>85894</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>118199</t>
+          <t>118496</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>164674</t>
+          <t>165093</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1062082</t>
+          <t>1064009</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1145113</t>
+          <t>1145712</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>911367</t>
+          <t>909479</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>986168</t>
+          <t>989529</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2001723</t>
+          <t>1996814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2114261</t>
+          <t>2108115</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,3%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>389201</t>
+          <t>390652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>461796</t>
+          <t>462066</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>399232</t>
+          <t>397107</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>468015</t>
+          <t>468676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>810865</t>
+          <t>808738</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>906310</t>
+          <t>913307</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72789</t>
+          <t>71520</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109259</t>
+          <t>109189</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>115808</t>
+          <t>114227</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160905</t>
+          <t>160209</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>196839</t>
+          <t>198123</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>254933</t>
+          <t>256646</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20311</t>
+          <t>20173</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43967</t>
+          <t>43580</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31040</t>
+          <t>30224</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37541</t>
+          <t>36301</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65578</t>
+          <t>65338</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>332010</t>
+          <t>329480</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>378277</t>
+          <t>378223</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>291577</t>
+          <t>289089</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>332962</t>
+          <t>331244</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>634867</t>
+          <t>633155</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>695566</t>
+          <t>695769</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,82%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120050</t>
+          <t>118591</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>161968</t>
+          <t>161573</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92492</t>
+          <t>92110</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>130557</t>
+          <t>129507</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>225039</t>
+          <t>225158</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>281339</t>
+          <t>283558</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15916</t>
+          <t>16444</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37917</t>
+          <t>39384</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20768</t>
+          <t>21622</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42613</t>
+          <t>43199</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>43420</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73745</t>
+          <t>74138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119808</t>
+          <t>118873</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>167617</t>
+          <t>168226</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>94447</t>
+          <t>94066</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>138099</t>
+          <t>135634</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>227742</t>
+          <t>226603</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>289295</t>
+          <t>289730</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1988877</t>
+          <t>1988644</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2095656</t>
+          <t>2093679</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1761971</t>
+          <t>1766797</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1879394</t>
+          <t>1883197</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3781441</t>
+          <t>3777222</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3943775</t>
+          <t>3942412</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,35%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>811254</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>913150</t>
+          <t>911320</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>953791</t>
+          <t>950884</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1060799</t>
+          <t>1066204</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1789579</t>
+          <t>1792627</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1942936</t>
+          <t>1941456</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>197318</t>
+          <t>197885</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>257772</t>
+          <t>253860</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>396227</t>
+          <t>389988</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>470841</t>
+          <t>469383</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>610066</t>
+          <t>606389</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>703342</t>
+          <t>704239</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción del peso respecto de su talla en 2012</t>
+          <t>Población según su autopercepción del peso respecto de su talla en 2012 (tasa de respuesta: 99,09%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36226</t>
+          <t>37051</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64365</t>
+          <t>65994</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29130</t>
+          <t>29520</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55036</t>
+          <t>55237</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72556</t>
+          <t>70322</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110163</t>
+          <t>111113</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>520261</t>
+          <t>521522</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>584744</t>
+          <t>587924</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>550909</t>
+          <t>547416</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>620959</t>
+          <t>622163</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1090966</t>
+          <t>1088599</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1188061</t>
+          <t>1188662</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,05%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>250669</t>
+          <t>253838</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311801</t>
+          <t>312322</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>478043</t>
+          <t>474917</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>548073</t>
+          <t>549125</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>751401</t>
+          <t>750997</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>842442</t>
+          <t>842236</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66275</t>
+          <t>63743</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101795</t>
+          <t>98867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>158275</t>
+          <t>155616</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>208109</t>
+          <t>207815</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>231598</t>
+          <t>232006</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>293182</t>
+          <t>292854</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77901</t>
+          <t>78538</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>116333</t>
+          <t>116657</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50114</t>
+          <t>51059</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>83978</t>
+          <t>84782</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>138826</t>
+          <t>137249</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>188711</t>
+          <t>189042</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1183619</t>
+          <t>1189953</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1273832</t>
+          <t>1277625</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>914631</t>
+          <t>921418</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1003736</t>
+          <t>1002403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2133962</t>
+          <t>2131027</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2256863</t>
+          <t>2254477</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,1%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>478139</t>
+          <t>482832</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>564835</t>
+          <t>557617</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514048</t>
+          <t>513561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>598948</t>
+          <t>595195</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1009977</t>
+          <t>1016514</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1130011</t>
+          <t>1134119</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,74%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81007</t>
+          <t>84351</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122760</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>137703</t>
+          <t>138932</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>186190</t>
+          <t>189704</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>230411</t>
+          <t>233166</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>297990</t>
+          <t>300830</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11717</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31420</t>
+          <t>30108</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40479</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34114</t>
+          <t>36211</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63918</t>
+          <t>64977</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>289101</t>
+          <t>292372</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>337934</t>
+          <t>336943</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>275938</t>
+          <t>277900</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>318948</t>
+          <t>322569</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>583125</t>
+          <t>582131</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>643736</t>
+          <t>645137</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,11%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97175</t>
+          <t>98003</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136382</t>
+          <t>138715</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86178</t>
+          <t>85313</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123417</t>
+          <t>122906</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>193362</t>
+          <t>191567</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>246709</t>
+          <t>248849</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>16710</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41432</t>
+          <t>40872</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15170</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>37610</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38712</t>
+          <t>36816</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69445</t>
+          <t>69332</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>140884</t>
+          <t>139167</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>193306</t>
+          <t>191170</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>113244</t>
+          <t>112100</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>162028</t>
+          <t>160589</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>266234</t>
+          <t>266293</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>334129</t>
+          <t>337806</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2042512</t>
+          <t>2043934</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2156224</t>
+          <t>2157751</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1784837</t>
+          <t>1784994</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1902008</t>
+          <t>1907104</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3861358</t>
+          <t>3857867</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4027044</t>
+          <t>4025164</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,28%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>867579</t>
+          <t>867846</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>971279</t>
+          <t>970498</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1116419</t>
+          <t>1111577</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1230893</t>
+          <t>1228791</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2013807</t>
+          <t>2001660</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2165054</t>
+          <t>2164491</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>181564</t>
+          <t>183453</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>242652</t>
+          <t>241017</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>330001</t>
+          <t>329060</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>408481</t>
+          <t>402341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>528943</t>
+          <t>526537</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>625563</t>
+          <t>624330</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción del peso respecto de su talla en 2016</t>
+          <t>Población según su autopercepción del peso respecto de su talla en 2016 (tasa de respuesta: 98,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19528</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40176</t>
+          <t>41584</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18276</t>
+          <t>17484</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41610</t>
+          <t>40421</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43989</t>
+          <t>41703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75048</t>
+          <t>71553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>391798</t>
+          <t>392141</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>445978</t>
+          <t>444480</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428384</t>
+          <t>426943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>495265</t>
+          <t>493787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>840937</t>
+          <t>841410</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>924461</t>
+          <t>923543</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,06%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>208185</t>
+          <t>203597</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>257597</t>
+          <t>253853</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>344165</t>
+          <t>341250</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>409989</t>
+          <t>406473</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>562595</t>
+          <t>564316</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>645122</t>
+          <t>645118</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45379</t>
+          <t>45463</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75406</t>
+          <t>74392</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89274</t>
+          <t>88768</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>130112</t>
+          <t>129376</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144740</t>
+          <t>142783</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>193765</t>
+          <t>194251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72672</t>
+          <t>72680</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>110960</t>
+          <t>111353</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67847</t>
+          <t>68260</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>102068</t>
+          <t>103205</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>148291</t>
+          <t>148239</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>197560</t>
+          <t>197924</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1279983</t>
+          <t>1282060</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1369900</t>
+          <t>1374741</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1142444</t>
+          <t>1143401</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1235444</t>
+          <t>1230819</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2448075</t>
+          <t>2452142</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2568697</t>
+          <t>2576017</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,92%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>490216</t>
+          <t>485948</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>571839</t>
+          <t>564929</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>501331</t>
+          <t>501591</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>582587</t>
+          <t>583599</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1016517</t>
+          <t>1015027</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1127255</t>
+          <t>1130301</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100129</t>
+          <t>98680</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146131</t>
+          <t>143487</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>130143</t>
+          <t>130073</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>178909</t>
+          <t>177693</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>242293</t>
+          <t>241608</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>308791</t>
+          <t>309765</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15062</t>
+          <t>15098</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36176</t>
+          <t>36742</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13858</t>
+          <t>13989</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32764</t>
+          <t>32908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34283</t>
+          <t>33200</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62677</t>
+          <t>59823</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>341879</t>
+          <t>343527</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>388270</t>
+          <t>389654</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>320932</t>
+          <t>323144</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>367742</t>
+          <t>367107</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>676854</t>
+          <t>677567</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>742459</t>
+          <t>744038</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,06%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103860</t>
+          <t>103704</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>143479</t>
+          <t>144324</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>118026</t>
+          <t>116925</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>158923</t>
+          <t>158979</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>231621</t>
+          <t>231844</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>291716</t>
+          <t>293062</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20172</t>
+          <t>20220</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45862</t>
+          <t>45127</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31384</t>
+          <t>31568</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57659</t>
+          <t>59180</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57975</t>
+          <t>59288</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>94596</t>
+          <t>94719</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120049</t>
+          <t>121158</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>168123</t>
+          <t>168912</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111435</t>
+          <t>110244</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>157304</t>
+          <t>156757</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>245081</t>
+          <t>246828</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>310760</t>
+          <t>312053</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2048264</t>
+          <t>2057422</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2168214</t>
+          <t>2164957</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1931267</t>
+          <t>1934417</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2050720</t>
+          <t>2054647</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4024589</t>
+          <t>4017397</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4190191</t>
+          <t>4183796</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,24%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>828787</t>
+          <t>827672</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>934693</t>
+          <t>931160</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>997883</t>
+          <t>1000764</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1107595</t>
+          <t>1108480</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1858544</t>
+          <t>1858823</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2013049</t>
+          <t>2008003</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>183504</t>
+          <t>182679</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>244117</t>
+          <t>243409</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>272278</t>
+          <t>273961</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>346764</t>
+          <t>342626</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>470749</t>
+          <t>468283</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>564087</t>
+          <t>561510</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción del peso respecto de su talla en 2023</t>
+          <t>Población según su autopercepción del peso respecto de su talla en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19514</t>
+          <t>19452</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39164</t>
+          <t>38693</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21673</t>
+          <t>21153</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38249</t>
+          <t>36931</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43471</t>
+          <t>44224</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69630</t>
+          <t>69564</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229546</t>
+          <t>229959</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272357</t>
+          <t>272976</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>350902</t>
+          <t>349542</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394076</t>
+          <t>394852</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>593118</t>
+          <t>595692</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>655430</t>
+          <t>655550</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>160902</t>
+          <t>163076</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>203603</t>
+          <t>205701</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>254706</t>
+          <t>255509</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>296186</t>
+          <t>295945</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>428018</t>
+          <t>430836</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>490305</t>
+          <t>487371</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40233</t>
+          <t>40544</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67545</t>
+          <t>66094</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63820</t>
+          <t>64297</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89412</t>
+          <t>90242</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111422</t>
+          <t>111114</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>148609</t>
+          <t>145595</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80051</t>
+          <t>78640</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>157499</t>
+          <t>153231</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>103185</t>
+          <t>101332</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>169735</t>
+          <t>169431</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>201072</t>
+          <t>202819</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>309116</t>
+          <t>307617</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>791161</t>
+          <t>861391</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1304654</t>
+          <t>1302536</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1261784</t>
+          <t>1268419</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1618244</t>
+          <t>1617876</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2130867</t>
+          <t>2127489</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2778884</t>
+          <t>2757905</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>60,96%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>695336</t>
+          <t>699595</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1320874</t>
+          <t>1247540</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>420661</t>
+          <t>421664</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657257</t>
+          <t>655032</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1225610</t>
+          <t>1239869</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2023742</t>
+          <t>2041857</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100175</t>
+          <t>104066</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>175391</t>
+          <t>177429</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100293</t>
+          <t>100941</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166064</t>
+          <t>167396</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>223751</t>
+          <t>225636</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>326244</t>
+          <t>328740</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22147</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44866</t>
+          <t>43744</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20349</t>
+          <t>19995</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39423</t>
+          <t>39032</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45439</t>
+          <t>45623</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75312</t>
+          <t>75044</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>353652</t>
+          <t>355095</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>406938</t>
+          <t>408925</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>380826</t>
+          <t>380320</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>425094</t>
+          <t>426589</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>752510</t>
+          <t>751636</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>823503</t>
+          <t>819858</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,72%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>175967</t>
+          <t>176135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>227513</t>
+          <t>225728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>162012</t>
+          <t>161315</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>202742</t>
+          <t>202279</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>350042</t>
+          <t>352578</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>414021</t>
+          <t>414758</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23724</t>
+          <t>23263</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44935</t>
+          <t>44506</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36911</t>
+          <t>37345</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60647</t>
+          <t>62264</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65626</t>
+          <t>63796</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>98322</t>
+          <t>97779</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>133069</t>
+          <t>135183</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>214837</t>
+          <t>220346</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>159542</t>
+          <t>160284</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>228042</t>
+          <t>227662</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>315740</t>
+          <t>315072</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>427483</t>
+          <t>426156</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1393689</t>
+          <t>1386853</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1938776</t>
+          <t>1937828</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2036577</t>
+          <t>2031797</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2429823</t>
+          <t>2424633</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3494868</t>
+          <t>3531081</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4203503</t>
+          <t>4206697</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,27%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1079475</t>
+          <t>1076733</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1720124</t>
+          <t>1730736</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>858558</t>
+          <t>843674</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1117344</t>
+          <t>1120416</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2061325</t>
+          <t>2052000</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2854528</t>
+          <t>2825503</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>39,81%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>182052</t>
+          <t>174989</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>267479</t>
+          <t>264196</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>214467</t>
+          <t>218646</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>298218</t>
+          <t>297216</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>421375</t>
+          <t>428657</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>541830</t>
+          <t>543284</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P47A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P47A-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28401</t>
+          <t>27967</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55390</t>
+          <t>54429</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17439</t>
+          <t>17351</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37716</t>
+          <t>36825</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52238</t>
+          <t>51049</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85337</t>
+          <t>85842</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>554891</t>
+          <t>550038</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>614548</t>
+          <t>613590</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>525147</t>
+          <t>520365</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>595036</t>
+          <t>597253</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1093069</t>
+          <t>1091903</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1190169</t>
+          <t>1189972</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,89%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>268791</t>
+          <t>266242</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>323342</t>
+          <t>321845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>429441</t>
+          <t>425533</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>497188</t>
+          <t>496174</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>711403</t>
+          <t>709302</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>802084</t>
+          <t>800665</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93617</t>
+          <t>93111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>135285</t>
+          <t>130459</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>237175</t>
+          <t>238378</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>296712</t>
+          <t>295073</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>341360</t>
+          <t>341508</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>410878</t>
+          <t>409072</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55736</t>
+          <t>55977</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92140</t>
+          <t>89603</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52555</t>
+          <t>52442</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>85894</t>
+          <t>85885</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>118496</t>
+          <t>118967</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>165093</t>
+          <t>163514</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1064009</t>
+          <t>1062628</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1145712</t>
+          <t>1140088</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>909479</t>
+          <t>911277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>989529</t>
+          <t>991253</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1996814</t>
+          <t>1999045</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2108115</t>
+          <t>2108053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>390652</t>
+          <t>389358</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>462066</t>
+          <t>464743</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,39 +1543,39 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>27,47%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>433332</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>396984</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>467665</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>27,31%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>433332</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>397107</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>468676</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>27,31%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>25,02%</t>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>808738</t>
+          <t>808429</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>913307</t>
+          <t>911852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71520</t>
+          <t>74239</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109189</t>
+          <t>108886</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>114227</t>
+          <t>113623</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160209</t>
+          <t>160711</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>198123</t>
+          <t>197593</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>256646</t>
+          <t>253775</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20173</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43580</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13246</t>
+          <t>13737</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30224</t>
+          <t>31590</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36301</t>
+          <t>38352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65338</t>
+          <t>66648</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>329480</t>
+          <t>330240</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>378223</t>
+          <t>377285</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>289089</t>
+          <t>290872</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>331244</t>
+          <t>332216</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>633155</t>
+          <t>633857</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>695769</t>
+          <t>696060</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,85%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>118591</t>
+          <t>120768</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>161573</t>
+          <t>162232</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92110</t>
+          <t>93807</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>129507</t>
+          <t>129290</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>225158</t>
+          <t>223909</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>283558</t>
+          <t>279993</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16444</t>
+          <t>16318</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39384</t>
+          <t>38268</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21622</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43199</t>
+          <t>41903</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43420</t>
+          <t>42988</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74138</t>
+          <t>73548</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>118873</t>
+          <t>116030</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>168226</t>
+          <t>166733</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>94066</t>
+          <t>94424</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>135634</t>
+          <t>137985</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>226603</t>
+          <t>227694</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>289730</t>
+          <t>289570</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1988644</t>
+          <t>1988561</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2093679</t>
+          <t>2096663</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1766797</t>
+          <t>1764177</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1883197</t>
+          <t>1873440</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3777222</t>
+          <t>3774568</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3942412</t>
+          <t>3940570</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>813950</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>911320</t>
+          <t>909062</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>950884</t>
+          <t>961857</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1066204</t>
+          <t>1061237</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1792627</t>
+          <t>1796744</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1941456</t>
+          <t>1944155</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>197885</t>
+          <t>196012</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>253860</t>
+          <t>252900</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>389988</t>
+          <t>392490</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>469383</t>
+          <t>469652</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>606389</t>
+          <t>611320</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>704239</t>
+          <t>714762</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37051</t>
+          <t>36125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65994</t>
+          <t>65955</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>28756</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55237</t>
+          <t>55020</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70322</t>
+          <t>71980</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111113</t>
+          <t>113762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>521522</t>
+          <t>523800</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>587924</t>
+          <t>584830</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>547416</t>
+          <t>549869</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>622163</t>
+          <t>623810</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1088599</t>
+          <t>1082683</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1188662</t>
+          <t>1184073</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,85%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>253838</t>
+          <t>255043</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>312322</t>
+          <t>313765</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>474917</t>
+          <t>479127</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>549125</t>
+          <t>546672</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>750997</t>
+          <t>749828</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>842236</t>
+          <t>846145</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63743</t>
+          <t>65364</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98867</t>
+          <t>101125</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155616</t>
+          <t>157992</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>207815</t>
+          <t>208689</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>232006</t>
+          <t>231783</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>292854</t>
+          <t>292185</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78538</t>
+          <t>79353</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>116657</t>
+          <t>116746</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51059</t>
+          <t>50255</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84782</t>
+          <t>85647</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>137249</t>
+          <t>138022</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>189042</t>
+          <t>187792</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1189953</t>
+          <t>1192015</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1277625</t>
+          <t>1275430</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>921418</t>
+          <t>917300</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1002403</t>
+          <t>1005553</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2131027</t>
+          <t>2130656</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2254477</t>
+          <t>2258200</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,21%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>482832</t>
+          <t>478197</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>557617</t>
+          <t>559357</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>513561</t>
+          <t>513117</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>595195</t>
+          <t>595821</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1016514</t>
+          <t>1013756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1134119</t>
+          <t>1129066</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84351</t>
+          <t>81399</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>121753</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>138932</t>
+          <t>137980</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>189704</t>
+          <t>188625</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>233166</t>
+          <t>231392</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>300830</t>
+          <t>295734</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12137</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30108</t>
+          <t>31665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19626</t>
+          <t>19246</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>41442</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36211</t>
+          <t>36044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64977</t>
+          <t>63918</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>292372</t>
+          <t>290632</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>336943</t>
+          <t>335613</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>277900</t>
+          <t>277126</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>322569</t>
+          <t>321016</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>582131</t>
+          <t>583003</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>645137</t>
+          <t>644767</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98003</t>
+          <t>96780</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>138715</t>
+          <t>136556</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85313</t>
+          <t>84957</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>122906</t>
+          <t>122530</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>191567</t>
+          <t>194112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>248849</t>
+          <t>251875</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16710</t>
+          <t>16358</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40872</t>
+          <t>39789</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37610</t>
+          <t>38026</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36816</t>
+          <t>37779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69332</t>
+          <t>69563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>139167</t>
+          <t>140533</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>191170</t>
+          <t>193522</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>112100</t>
+          <t>114229</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>160589</t>
+          <t>162995</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>266293</t>
+          <t>264377</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>337806</t>
+          <t>337340</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2043934</t>
+          <t>2038575</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2157751</t>
+          <t>2160663</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1784994</t>
+          <t>1784215</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1907104</t>
+          <t>1907301</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3857867</t>
+          <t>3856588</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4025164</t>
+          <t>4025300</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>867846</t>
+          <t>863394</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>970498</t>
+          <t>971236</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1111577</t>
+          <t>1113019</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1228791</t>
+          <t>1228394</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2001660</t>
+          <t>2012268</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2164491</t>
+          <t>2169911</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>183453</t>
+          <t>179137</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>241017</t>
+          <t>239896</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>329060</t>
+          <t>329847</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>402341</t>
+          <t>406412</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>526537</t>
+          <t>529258</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>624330</t>
+          <t>625609</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20458</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41584</t>
+          <t>41029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17484</t>
+          <t>17918</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40421</t>
+          <t>41305</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41703</t>
+          <t>42164</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71553</t>
+          <t>73134</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>392141</t>
+          <t>394613</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>444480</t>
+          <t>444451</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>426943</t>
+          <t>432847</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>493787</t>
+          <t>497543</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>841410</t>
+          <t>836177</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>923543</t>
+          <t>922410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>203597</t>
+          <t>203589</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>253853</t>
+          <t>252426</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>341250</t>
+          <t>340929</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>406473</t>
+          <t>403710</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>564316</t>
+          <t>560070</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>645118</t>
+          <t>645698</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,8%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45463</t>
+          <t>45651</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74392</t>
+          <t>75109</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88768</t>
+          <t>89297</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>129376</t>
+          <t>129358</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142783</t>
+          <t>143553</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>194251</t>
+          <t>194429</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72680</t>
+          <t>71766</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111353</t>
+          <t>112917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68260</t>
+          <t>66377</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>103205</t>
+          <t>102599</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>148239</t>
+          <t>148147</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>197924</t>
+          <t>202463</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1282060</t>
+          <t>1282698</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1374741</t>
+          <t>1373974</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1143401</t>
+          <t>1140422</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1230819</t>
+          <t>1231068</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2452142</t>
+          <t>2449171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2576017</t>
+          <t>2577667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>485948</t>
+          <t>484124</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>564929</t>
+          <t>569888</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>501591</t>
+          <t>503984</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>583599</t>
+          <t>581176</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1015027</t>
+          <t>1011462</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1130301</t>
+          <t>1123801</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98680</t>
+          <t>101684</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>143487</t>
+          <t>145101</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>130073</t>
+          <t>128853</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>177693</t>
+          <t>179118</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>241608</t>
+          <t>242210</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>309765</t>
+          <t>309380</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15098</t>
+          <t>15020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36742</t>
+          <t>34357</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13989</t>
+          <t>13435</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32908</t>
+          <t>32086</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33200</t>
+          <t>34762</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59823</t>
+          <t>62282</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>343527</t>
+          <t>344650</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>389654</t>
+          <t>387542</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>323144</t>
+          <t>321671</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>367107</t>
+          <t>368726</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>677567</t>
+          <t>679906</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>744038</t>
+          <t>745835</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,23%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103704</t>
+          <t>104016</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>144324</t>
+          <t>143471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>116925</t>
+          <t>117086</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>158979</t>
+          <t>157205</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>231844</t>
+          <t>232454</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>293062</t>
+          <t>291608</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20220</t>
+          <t>20228</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45127</t>
+          <t>44941</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31568</t>
+          <t>31742</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59180</t>
+          <t>60449</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59288</t>
+          <t>58593</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>94719</t>
+          <t>94668</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>121158</t>
+          <t>118434</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>168912</t>
+          <t>167234</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>110244</t>
+          <t>112067</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>156757</t>
+          <t>158585</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>246828</t>
+          <t>242987</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>312053</t>
+          <t>308490</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2057422</t>
+          <t>2056761</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2164957</t>
+          <t>2169200</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1934417</t>
+          <t>1936188</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2054647</t>
+          <t>2052659</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4017397</t>
+          <t>4023235</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4183796</t>
+          <t>4191237</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,35%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>827672</t>
+          <t>832865</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>931160</t>
+          <t>937396</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1000764</t>
+          <t>1000666</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1108480</t>
+          <t>1109883</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1858823</t>
+          <t>1855606</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2008003</t>
+          <t>2003409</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>182679</t>
+          <t>180986</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>243409</t>
+          <t>237573</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>273961</t>
+          <t>274907</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>342626</t>
+          <t>342075</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>468283</t>
+          <t>474842</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>561510</t>
+          <t>569178</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28018</t>
+          <t>29372</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19452</t>
+          <t>20762</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38693</t>
+          <t>41751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28187</t>
+          <t>30691</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21153</t>
+          <t>22706</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36931</t>
+          <t>40448</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>56205</t>
+          <t>60063</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44224</t>
+          <t>48137</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69564</t>
+          <t>75601</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>251922</t>
+          <t>299171</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229959</t>
+          <t>275523</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272976</t>
+          <t>322138</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>373253</t>
+          <t>408379</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>349542</t>
+          <t>387144</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394852</t>
+          <t>433284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>625175</t>
+          <t>707550</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>595692</t>
+          <t>675503</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>655550</t>
+          <t>744409</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>53,3%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>181759</t>
+          <t>190731</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>163076</t>
+          <t>170893</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>205701</t>
+          <t>214308</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>275175</t>
+          <t>296740</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>255509</t>
+          <t>275113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>295945</t>
+          <t>317671</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>456935</t>
+          <t>487471</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>430836</t>
+          <t>454003</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>487371</t>
+          <t>516003</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52375</t>
+          <t>58314</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40544</t>
+          <t>44951</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66094</t>
+          <t>73128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>76177</t>
+          <t>83227</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64297</t>
+          <t>70649</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90242</t>
+          <t>97072</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>128553</t>
+          <t>141541</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111114</t>
+          <t>120903</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145595</t>
+          <t>159874</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514074</t>
+          <t>577588</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514074</t>
+          <t>577588</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514074</t>
+          <t>577588</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>752792</t>
+          <t>819038</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>752792</t>
+          <t>819038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>752792</t>
+          <t>819038</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1266867</t>
+          <t>1396626</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1266867</t>
+          <t>1396626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1266867</t>
+          <t>1396626</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>116882</t>
+          <t>126796</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78640</t>
+          <t>101652</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>153231</t>
+          <t>159084</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>138538</t>
+          <t>150881</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>101332</t>
+          <t>129469</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>169431</t>
+          <t>180180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>255420</t>
+          <t>277677</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>202819</t>
+          <t>238637</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>307617</t>
+          <t>318776</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1143820</t>
+          <t>1255086</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>861391</t>
+          <t>1194518</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1302536</t>
+          <t>1303181</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1381427</t>
+          <t>1216117</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1268419</t>
+          <t>1164345</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1617876</t>
+          <t>1255773</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2525246</t>
+          <t>2471203</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2127489</t>
+          <t>2395929</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2757905</t>
+          <t>2538619</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>57,73%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>883874</t>
+          <t>693371</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>699595</t>
+          <t>648361</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1247540</t>
+          <t>756293</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>575867</t>
+          <t>646798</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>421664</t>
+          <t>608262</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>655032</t>
+          <t>685196</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1459741</t>
+          <t>1340169</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1239869</t>
+          <t>1279636</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2041857</t>
+          <t>1403206</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>143995</t>
+          <t>153321</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104066</t>
+          <t>128668</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>177429</t>
+          <t>180268</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>139436</t>
+          <t>154907</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100941</t>
+          <t>135627</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>167396</t>
+          <t>178987</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>283431</t>
+          <t>308228</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>225636</t>
+          <t>274627</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>328740</t>
+          <t>338719</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2288571</t>
+          <t>2228574</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2288571</t>
+          <t>2228574</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2288571</t>
+          <t>2228574</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2235267</t>
+          <t>2168703</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2235267</t>
+          <t>2168703</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2235267</t>
+          <t>2168703</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4523837</t>
+          <t>4397277</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4523837</t>
+          <t>4397277</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4523837</t>
+          <t>4397277</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31254</t>
+          <t>35442</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20237</t>
+          <t>25148</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43744</t>
+          <t>49249</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>28089</t>
+          <t>35400</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19995</t>
+          <t>25292</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39032</t>
+          <t>49396</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>59343</t>
+          <t>70842</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45623</t>
+          <t>55241</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75044</t>
+          <t>88775</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>380986</t>
+          <t>425591</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>355095</t>
+          <t>397205</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>408925</t>
+          <t>456407</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>404482</t>
+          <t>443289</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>380320</t>
+          <t>417872</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>426589</t>
+          <t>467416</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>785468</t>
+          <t>868880</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>751636</t>
+          <t>830419</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>819858</t>
+          <t>904842</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,56%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>201817</t>
+          <t>216269</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>176135</t>
+          <t>186759</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>225728</t>
+          <t>243065</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>180488</t>
+          <t>203249</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>161315</t>
+          <t>181489</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>202279</t>
+          <t>225042</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>382305</t>
+          <t>419518</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>352578</t>
+          <t>385975</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>414758</t>
+          <t>454806</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32566</t>
+          <t>34285</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23263</t>
+          <t>24397</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44506</t>
+          <t>47282</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>47405</t>
+          <t>52939</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37345</t>
+          <t>40778</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62264</t>
+          <t>66610</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>79971</t>
+          <t>87224</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63796</t>
+          <t>72639</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>97779</t>
+          <t>108050</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,67 +9956,67 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>176154</t>
+          <t>191610</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>135183</t>
+          <t>161785</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>220346</t>
+          <t>230249</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>5,45%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>216972</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>190093</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>249318</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>5,11%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>194813</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>160284</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>227662</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>370967</t>
+          <t>408583</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>315072</t>
+          <t>369305</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>426156</t>
+          <t>459745</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1776727</t>
+          <t>1979847</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1386853</t>
+          <t>1915521</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1937828</t>
+          <t>2042140</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2159161</t>
+          <t>2067786</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2031797</t>
+          <t>2010009</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2424633</t>
+          <t>2116285</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3935888</t>
+          <t>4047633</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3531081</t>
+          <t>3960454</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4206697</t>
+          <t>4137165</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1267450</t>
+          <t>1100372</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1076733</t>
+          <t>1041289</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1730736</t>
+          <t>1165652</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1031530</t>
+          <t>1146787</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>843674</t>
+          <t>1098404</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1120416</t>
+          <t>1199905</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2298981</t>
+          <t>2247159</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2052000</t>
+          <t>2169011</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2825503</t>
+          <t>2324629</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>228937</t>
+          <t>245920</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>174989</t>
+          <t>213986</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>264196</t>
+          <t>276774</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>263017</t>
+          <t>291074</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>218646</t>
+          <t>265082</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>297216</t>
+          <t>322583</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>491954</t>
+          <t>536994</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>428657</t>
+          <t>495867</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>543284</t>
+          <t>580349</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3449268</t>
+          <t>3517749</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3449268</t>
+          <t>3517749</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3449268</t>
+          <t>3517749</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3648522</t>
+          <t>3722619</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3648522</t>
+          <t>3722619</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3648522</t>
+          <t>3722619</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7097790</t>
+          <t>7240368</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7097790</t>
+          <t>7240368</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7097790</t>
+          <t>7240368</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
